--- a/salesforce_forms/002_custom_t_shirt_order_form_template--salesforce_forms.xlsx
+++ b/salesforce_forms/002_custom_t_shirt_order_form_template--salesforce_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -643,7 +643,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>t_shirt_color</t>
+          <t>t_shirt_color_2</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>order_notes</t>
+          <t>order_notes_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -988,7 +988,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Customer name</t>
+          <t>Customer Name 3</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1034,12 +1034,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>customer_name</t>
+          <t>customer_name_4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Customer name</t>
+          <t>Customer Name 4</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1057,12 +1057,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>customer_phone</t>
+          <t>customer_phone_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Customer phone</t>
+          <t>Customer Phone 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>customer_email</t>
+          <t>customer_email_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Customer email</t>
+          <t>Customer Email 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
